--- a/src/generated_files/MP3Tag_Mappings.xlsx
+++ b/src/generated_files/MP3Tag_Mappings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\src\generated_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{318F2DC7-7B78-4132-8169-BA8DA33C09B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FA0A163-3634-43FE-A376-CCB5E11800F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{734FDB5F-9A0D-4C22-83E5-5754F2D1B3BA}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="260">
   <si>
     <t>Name in Mp3tag</t>
   </si>
@@ -304,9 +304,6 @@
   </si>
   <si>
     <t>TCON</t>
-  </si>
-  <si>
-    <t>©gen | gnre</t>
   </si>
   <si>
     <t>WM/Genre</t>
@@ -822,6 +819,54 @@
   </si>
   <si>
     <t>NOT the same thing as MP4 desc</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:MEDIA</t>
+  </si>
+  <si>
+    <t>WM/Media</t>
+  </si>
+  <si>
+    <t>ART</t>
+  </si>
+  <si>
+    <t>APIC</t>
+  </si>
+  <si>
+    <t>cover</t>
+  </si>
+  <si>
+    <t>WM/Picture</t>
+  </si>
+  <si>
+    <t>©too</t>
+  </si>
+  <si>
+    <t>©gen</t>
+  </si>
+  <si>
+    <t>rtng</t>
+  </si>
+  <si>
+    <t>https://docs.mp3tag.de/mapping-table/</t>
+  </si>
+  <si>
+    <t>https://ffmpeg.org/doxygen/trunk/group__metadata__api.html</t>
+  </si>
+  <si>
+    <t>https://wiki.multimedia.cx/index.php?title=FFmpeg_Metadata</t>
+  </si>
+  <si>
+    <t>https://gist.github.com/eyecatchup/0757b3d8b989fe433979db2ea7d95a01</t>
+  </si>
+  <si>
+    <t>https://github.com/sergiomb2/libmp4v2/wiki/iTunesMetadata</t>
+  </si>
+  <si>
+    <t>https://atomicparsley.sourceforge.net/mpeg-4files.html</t>
+  </si>
+  <si>
+    <t>http://ffmpeg.org/pipermail/ffmpeg-user/attachments/20181208/87040191/attachment.obj dl and rename obj to xlsx</t>
   </si>
 </sst>
 </file>
@@ -971,10 +1016,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -984,7 +1028,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1006,7 +1050,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1022,6 +1066,13 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1337,1263 +1388,1302 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2156D25B-3C27-4FF6-8D3E-055BF1FDA5A8}">
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="23.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="121.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="3" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="121.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="14"/>
-      <c r="F2" s="6"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="5" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="14"/>
-      <c r="F3" s="6"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="5" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="6"/>
+      <c r="F4" s="5" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="7"/>
+      <c r="F5" s="5" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="7"/>
+      <c r="F6" s="5" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="13"/>
-      <c r="F7" s="7"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="5" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E9" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="7"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="F9" s="6"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D10" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E10" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F9" s="7"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="F10" s="6"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D11" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E11" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F10" s="7"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="F11" s="6"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D12" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E12" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F12" s="6" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" s="6"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E15" s="12"/>
+      <c r="F15" s="6"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F16" s="6"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" s="6"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F18" s="6"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D19" s="11"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="6"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="B20" s="10"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" s="12"/>
+      <c r="F20" s="6" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F21" s="6"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F22" s="6"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D23" t="s">
+        <v>250</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F23" s="6"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="B24" s="10"/>
+      <c r="C24" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D24" s="11"/>
+      <c r="E24" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F24" s="6"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D25" s="11"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="6"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D26" s="11"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="6"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F27" s="6"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D28" s="11"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="6"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D29" s="6"/>
+      <c r="E29" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F29" s="6"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D30" s="11"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D31" s="11"/>
+      <c r="E31" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="F31" s="6"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D32" s="11"/>
+      <c r="E32" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F32" s="6"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D33" s="11"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="6"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D34" s="11"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="6"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D35" s="19" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E12" s="18" t="s">
-        <v>239</v>
-      </c>
-      <c r="F12" s="7" t="s">
+      <c r="E35" s="19" t="s">
+        <v>245</v>
+      </c>
+      <c r="F35" s="6"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D36" s="11"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="6"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="B37" s="10"/>
+      <c r="C37" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="D37" s="18" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="F13" s="7"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="E14" s="13"/>
-      <c r="F14" s="7"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="F15" s="7"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="F16" s="7"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F17" s="7"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D18" s="12"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="7"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E19" s="13"/>
-      <c r="F19" s="7" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="F20" s="7"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="F21" s="7"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="D22" s="7"/>
-      <c r="E22" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="F22" s="7"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="B23" s="11"/>
-      <c r="C23" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="D23" s="12"/>
-      <c r="E23" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="F23" s="7"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="D24" s="12"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="7"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D25" s="12"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="7"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="F26" s="7"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="D27" s="12"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="7"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D28" s="7"/>
-      <c r="E28" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="F28" s="7"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C29" s="5" t="s">
+      <c r="E37" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E38" s="12"/>
+      <c r="F38" s="6"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E39" s="12"/>
+      <c r="F39" s="6"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E40" s="12"/>
+      <c r="F40" s="6"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="B41" s="10"/>
+      <c r="C41" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D41" s="11"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="D29" s="12"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="7" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="D30" s="12"/>
-      <c r="E30" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="F30" s="7"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="D31" s="12"/>
-      <c r="E31" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="F31" s="7"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="D32" s="12"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="7"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D33" s="12"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="7"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="D34" s="12"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="7"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D35" s="12"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="7"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="B36" s="11"/>
-      <c r="C36" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="D36" s="19" t="s">
-        <v>241</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="E37" s="13"/>
-      <c r="F37" s="7"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="E38" s="13"/>
-      <c r="F38" s="7"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="E39" s="13"/>
-      <c r="F39" s="7"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="B40" s="11"/>
-      <c r="C40" s="5" t="s">
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="D40" s="12"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="7" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="16" t="s">
+      <c r="B42" s="10"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B41" s="11"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="5" t="s">
+      <c r="E42" s="12"/>
+      <c r="F42" s="6"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="E41" s="13"/>
-      <c r="F41" s="7"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="16" t="s">
+      <c r="B43" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="C43" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D43" s="11"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="6"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="C42" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="D42" s="12"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="7"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="16" t="s">
+      <c r="B44" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="C44" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D44" s="11"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="6"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="C43" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="D43" s="12"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="7"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="16" t="s">
+      <c r="B45" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="C45" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D45" s="11"/>
+      <c r="E45" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="C44" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="D44" s="12"/>
-      <c r="E44" s="5" t="s">
+      <c r="F45" s="6"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="F44" s="7"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="16" t="s">
+      <c r="B46" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="C46" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D46" s="11"/>
+      <c r="E46" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="C45" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="D45" s="12"/>
-      <c r="E45" s="5" t="s">
+      <c r="F46" s="6"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="F45" s="7"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="16" t="s">
+      <c r="B47" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="C47" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D47" s="11"/>
+      <c r="E47" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="C46" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="D46" s="12"/>
-      <c r="E46" s="5" t="s">
+      <c r="F47" s="6"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="F46" s="7"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="16" t="s">
+      <c r="B48" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="C48" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D48" s="11"/>
+      <c r="E48" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="C47" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="D47" s="12"/>
-      <c r="E47" s="5" t="s">
+      <c r="F48" s="6"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="F47" s="7"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="16" t="s">
+      <c r="B49" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="C49" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="8" t="s">
+      <c r="D49" s="11"/>
+      <c r="E49" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="D48" s="12"/>
-      <c r="E48" s="5" t="s">
+      <c r="F49" s="6"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="F48" s="7"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="16" t="s">
+      <c r="B50" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="C50" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="D50" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="C49" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="D49" s="5" t="s">
+      <c r="E50" s="12"/>
+      <c r="F50" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="E49" s="13"/>
-      <c r="F49" s="7" t="s">
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="15" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="16" t="s">
+      <c r="B51" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="C51" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="D51" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="C50" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="D50" s="5" t="s">
+      <c r="E51" s="12"/>
+      <c r="F51" s="6"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="E50" s="13"/>
-      <c r="F50" s="7"/>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="16" t="s">
+      <c r="B52" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="C52" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D52" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="C51" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="D51" s="5" t="s">
+      <c r="E52" s="12"/>
+      <c r="F52" s="6"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="E51" s="13"/>
-      <c r="F51" s="7"/>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="16" t="s">
+      <c r="B53" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="C53" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="D53" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="C52" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="D52" s="5" t="s">
+      <c r="E53" s="12"/>
+      <c r="F53" s="6"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="E52" s="13"/>
-      <c r="F52" s="7"/>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="16" t="s">
+      <c r="B54" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="C54" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D54" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="C53" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="D53" s="5" t="s">
+      <c r="E54" s="12"/>
+      <c r="F54" s="6"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="E53" s="13"/>
-      <c r="F53" s="7"/>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="16" t="s">
+      <c r="B55" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="C55" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D55" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="C54" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="D54" s="5" t="s">
+      <c r="E55" s="12"/>
+      <c r="F55" s="6"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="E54" s="13"/>
-      <c r="F54" s="7"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="16" t="s">
+      <c r="B56" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="C56" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="D56" s="11"/>
+      <c r="E56" s="12"/>
+      <c r="F56" s="6" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="C55" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="D55" s="12"/>
-      <c r="E55" s="13"/>
-      <c r="F55" s="7" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="4" t="s">
+      <c r="B57" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="C57" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D57" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="C56" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="D56" s="5" t="s">
+      <c r="E57" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="E56" s="5" t="s">
+      <c r="F57" s="6"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="F56" s="7"/>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="16" t="s">
+      <c r="B58" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="D58" s="20" t="s">
+        <v>252</v>
+      </c>
+      <c r="E58" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="B57" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="D57" s="12"/>
-      <c r="E57" s="5" t="s">
+      <c r="F58" s="6" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="F57" s="7" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="16" t="s">
+      <c r="B59" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="C59" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="D59" s="11"/>
+      <c r="E59" s="12"/>
+      <c r="F59" s="6"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="C58" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="D58" s="12"/>
-      <c r="E58" s="13"/>
-      <c r="F58" s="7"/>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="16" t="s">
+      <c r="B60" s="10"/>
+      <c r="C60" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="B59" s="11"/>
-      <c r="C59" s="10" t="s">
+      <c r="D60" s="11"/>
+      <c r="E60" s="12"/>
+      <c r="F60" s="6"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="D59" s="12"/>
-      <c r="E59" s="13"/>
-      <c r="F59" s="7"/>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="16" t="s">
+      <c r="B61" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="C61" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="D61" s="11"/>
+      <c r="E61" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="C60" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="D60" s="12"/>
-      <c r="E60" s="5" t="s">
+      <c r="F61" s="6"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="F60" s="7"/>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="16" t="s">
+      <c r="B62" s="10"/>
+      <c r="C62" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="B61" s="11"/>
-      <c r="C61" s="10" t="s">
+      <c r="D62" s="11"/>
+      <c r="E62" s="12"/>
+      <c r="F62" s="6"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="D61" s="12"/>
-      <c r="E61" s="13"/>
-      <c r="F61" s="7"/>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="4" t="s">
+      <c r="B63" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="B62" s="5" t="s">
+      <c r="C63" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="D63" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="C62" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="D62" s="5" t="s">
+      <c r="E63" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="E62" s="5" t="s">
+      <c r="F63" s="6"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="F62" s="7"/>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="4" t="s">
+      <c r="B64" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="B63" s="5" t="s">
+      <c r="C64" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="D64" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="C63" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="D63" s="5" t="s">
+      <c r="E64" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="E63" s="5" t="s">
+      <c r="F64" s="6"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="F63" s="7"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="4" t="s">
+      <c r="B65" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="B64" s="5" t="s">
+      <c r="C65" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D65" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="C64" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="D64" s="5" t="s">
+      <c r="E65" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="E64" s="5" t="s">
+      <c r="F65" s="6"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="F64" s="7"/>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="16" t="s">
+      <c r="B66" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="B65" s="5" t="s">
+      <c r="C66" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="D66" s="11"/>
+      <c r="E66" s="12"/>
+      <c r="F66" s="6"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="C65" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="D65" s="12"/>
-      <c r="E65" s="13"/>
-      <c r="F65" s="7"/>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="4" t="s">
+      <c r="B67" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="B66" s="5" t="s">
+      <c r="C67" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="D67" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="C66" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D66" s="5" t="s">
+      <c r="E67" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="E66" s="5" t="s">
+      <c r="F67" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="F66" s="7" t="s">
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="15" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="16" t="s">
+      <c r="B68" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="B67" s="5" t="s">
+      <c r="C68" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D68" s="11"/>
+      <c r="E68" s="12"/>
+      <c r="F68" s="6"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="15" t="s">
         <v>206</v>
       </c>
-      <c r="C67" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="D67" s="12"/>
-      <c r="E67" s="13"/>
-      <c r="F67" s="7"/>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="16" t="s">
+      <c r="B69" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="B68" s="5" t="s">
+      <c r="C69" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="D69" s="11"/>
+      <c r="E69" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="C68" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="D68" s="12"/>
-      <c r="E68" s="5" t="s">
+      <c r="F69" s="6"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="15" t="s">
         <v>209</v>
       </c>
-      <c r="F68" s="7"/>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="16" t="s">
+      <c r="B70" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="B69" s="5" t="s">
+      <c r="C70" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="D70" s="11"/>
+      <c r="E70" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="C69" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="D69" s="12"/>
-      <c r="E69" s="5" t="s">
+      <c r="F70" s="6"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="15" t="s">
         <v>212</v>
       </c>
-      <c r="F69" s="7"/>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="16" t="s">
+      <c r="B71" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="B70" s="5" t="s">
+      <c r="C71" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="D71" s="11"/>
+      <c r="E71" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="C70" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="D70" s="12"/>
-      <c r="E70" s="5" t="s">
+      <c r="F71" s="6"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="F70" s="7"/>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="16" t="s">
+      <c r="B72" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="B71" s="5" t="s">
+      <c r="C72" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="D72" s="11"/>
+      <c r="E72" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="C71" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="D71" s="12"/>
-      <c r="E71" s="5" t="s">
+      <c r="F72" s="6"/>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="F71" s="7"/>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="16" t="s">
+      <c r="B73" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="B72" s="5" t="s">
+      <c r="C73" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="D73" s="11"/>
+      <c r="E73" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="C72" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="D72" s="12"/>
-      <c r="E72" s="5" t="s">
+      <c r="F73" s="6"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="F72" s="7"/>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="16" t="s">
+      <c r="B74" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="B73" s="5" t="s">
+      <c r="C74" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="D74" s="11"/>
+      <c r="E74" s="12"/>
+      <c r="F74" s="6"/>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="C73" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="D73" s="12"/>
-      <c r="E73" s="13"/>
-      <c r="F73" s="7"/>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="16" t="s">
+      <c r="B75" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B74" s="5" t="s">
+      <c r="C75" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="D75" s="11"/>
+      <c r="E75" s="12"/>
+      <c r="F75" s="6"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="15" t="s">
         <v>225</v>
       </c>
-      <c r="C74" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="D74" s="12"/>
-      <c r="E74" s="13"/>
-      <c r="F74" s="7"/>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="16" t="s">
+      <c r="B76" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="B75" s="5" t="s">
+      <c r="C76" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="D76" s="11"/>
+      <c r="E76" s="12"/>
+      <c r="F76" s="6"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="C75" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="D75" s="12"/>
-      <c r="E75" s="13"/>
-      <c r="F75" s="7"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="4" t="s">
+      <c r="B77" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="B76" s="8" t="s">
+      <c r="C77" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="C76" s="8" t="s">
+      <c r="D77" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="D76" s="5" t="s">
+      <c r="E77" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="E76" s="5" t="s">
+      <c r="F77" s="6"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="F76" s="7"/>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="4" t="s">
+      <c r="B78" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="B77" s="5" t="s">
+      <c r="C78" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="D78" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="C77" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="D77" s="5" t="s">
+      <c r="E78" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="E77" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="F77" s="7"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="3"/>
-    </row>
-    <row r="79" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F78" s="6"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="2"/>
+    </row>
+    <row r="80" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A80" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2603,76 +2693,77 @@
     <hyperlink ref="A5" r:id="rId4" location="albumsort" display="https://docs.mp3tag.de/mapping-table/ - albumsort" xr:uid="{DC64BBE5-689F-40D4-BE30-8B9F0CD0AA0A}"/>
     <hyperlink ref="A6" r:id="rId5" location="albumartist" display="https://docs.mp3tag.de/mapping-table/ - albumartist" xr:uid="{2382029C-7737-41D2-AEBF-F5F8138E079F}"/>
     <hyperlink ref="A7" r:id="rId6" location="albumartistsort" display="https://docs.mp3tag.de/mapping-table/ - albumartistsort" xr:uid="{7F040A69-4F71-4279-BE9C-681E610DD176}"/>
-    <hyperlink ref="A8" r:id="rId7" location="artist" display="https://docs.mp3tag.de/mapping-table/ - artist" xr:uid="{236B4608-7E32-4791-82B8-461C2ED1E009}"/>
-    <hyperlink ref="A9" r:id="rId8" location="artistsort" display="https://docs.mp3tag.de/mapping-table/ - artistsort" xr:uid="{F7E32035-C4EE-47AD-AB96-5FFB1EE40B6E}"/>
-    <hyperlink ref="A10" r:id="rId9" location="bpm" display="https://docs.mp3tag.de/mapping-table/ - bpm" xr:uid="{417BD8A8-54C5-4CA8-83B7-DD44A0D62B9D}"/>
-    <hyperlink ref="A11" r:id="rId10" location="comment" display="https://docs.mp3tag.de/mapping-table/ - comment" xr:uid="{EC4C54EF-C90D-48CF-8E6D-F63990567046}"/>
-    <hyperlink ref="A12" r:id="rId11" location="compilation" display="https://docs.mp3tag.de/mapping-table/ - compilation" xr:uid="{6767F38C-7169-4224-AFB8-A2FB203B1765}"/>
-    <hyperlink ref="A13" r:id="rId12" location="composer" display="https://docs.mp3tag.de/mapping-table/ - composer" xr:uid="{F59BF3E6-5073-42E9-BABC-679118C66E9A}"/>
-    <hyperlink ref="A14" r:id="rId13" location="composersort" display="https://docs.mp3tag.de/mapping-table/ - composersort" xr:uid="{EA1C71C2-F1C1-4694-9360-8205B00E8EA9}"/>
-    <hyperlink ref="A15" r:id="rId14" location="conductor" display="https://docs.mp3tag.de/mapping-table/ - conductor" xr:uid="{938268DC-3D45-4CE9-AE53-1A16ADBD5E92}"/>
-    <hyperlink ref="A16" r:id="rId15" location="contentgroup" display="https://docs.mp3tag.de/mapping-table/ - contentgroup" xr:uid="{325795C6-8803-429C-B96B-1EE71D190774}"/>
-    <hyperlink ref="A17" r:id="rId16" location="copyright" display="https://docs.mp3tag.de/mapping-table/ - copyright" xr:uid="{ECE81421-7610-4DC4-A813-351A7D2DF86F}"/>
-    <hyperlink ref="A18" r:id="rId17" location="date" display="https://docs.mp3tag.de/mapping-table/ - date" xr:uid="{C6D0C948-83BA-4EA8-8E18-B41689071623}"/>
-    <hyperlink ref="A19" r:id="rId18" location="description" display="https://docs.mp3tag.de/mapping-table/ - description" xr:uid="{92DAA412-9AE3-40D7-9EC5-21C4E42A776A}"/>
-    <hyperlink ref="A20" r:id="rId19" location="discnumber" display="https://docs.mp3tag.de/mapping-table/ - discnumber" xr:uid="{40CCC2AF-B3A2-4C9F-9DBF-27338C7896EA}"/>
-    <hyperlink ref="A21" r:id="rId20" location="encodedby" display="https://docs.mp3tag.de/mapping-table/ - encodedby" xr:uid="{4AB3273E-8541-486F-ABFF-C983DC6AE843}"/>
-    <hyperlink ref="A22" r:id="rId21" location="encodersettings" display="https://docs.mp3tag.de/mapping-table/ - encodersettings" xr:uid="{649B9604-04F5-4FE7-9842-5E27EFAE13E9}"/>
-    <hyperlink ref="A23" r:id="rId22" location="encodingtime" display="https://docs.mp3tag.de/mapping-table/ - encodingtime" xr:uid="{2AA00A50-84DF-4B28-B1CD-47E32FFBD2E9}"/>
-    <hyperlink ref="A24" r:id="rId23" location="fileowner" display="https://docs.mp3tag.de/mapping-table/ - fileowner" xr:uid="{B2201482-05EB-4062-A3F1-7FF04270E1E6}"/>
-    <hyperlink ref="A25" r:id="rId24" location="filetype" display="https://docs.mp3tag.de/mapping-table/ - filetype" xr:uid="{A18848A7-32AD-4B93-8679-B4FACBF6B1F0}"/>
-    <hyperlink ref="A26" r:id="rId25" location="genre" display="https://docs.mp3tag.de/mapping-table/ - genre" xr:uid="{06F89C2D-E212-45FA-95F6-ED590312B1AF}"/>
-    <hyperlink ref="A27" r:id="rId26" location="grouping" display="https://docs.mp3tag.de/mapping-table/ - grouping" xr:uid="{32419C34-9D9D-44BF-8A04-38F95F4C0E8F}"/>
-    <hyperlink ref="A28" r:id="rId27" location="initialkey" display="https://docs.mp3tag.de/mapping-table/ - initialkey" xr:uid="{D5949161-FC64-4D97-9683-CD512F59BBE5}"/>
-    <hyperlink ref="A29" r:id="rId28" location="involvedpeople" display="https://docs.mp3tag.de/mapping-table/ - involvedpeople" xr:uid="{29B7C220-BDD5-4964-A2CD-D239D4AFB52C}"/>
-    <hyperlink ref="A30" r:id="rId29" location="isrc" display="https://docs.mp3tag.de/mapping-table/ - isrc" xr:uid="{7B9290C2-318D-4750-B2D8-0254EC4D9E19}"/>
-    <hyperlink ref="A31" r:id="rId30" location="language" display="https://docs.mp3tag.de/mapping-table/ - language" xr:uid="{FD666EB8-5DD8-4502-A23A-37E947DECDBD}"/>
-    <hyperlink ref="A32" r:id="rId31" location="length" display="https://docs.mp3tag.de/mapping-table/ - length" xr:uid="{A6E54695-7179-42BB-AE44-2501173B82AA}"/>
-    <hyperlink ref="A33" r:id="rId32" location="lyricist" display="https://docs.mp3tag.de/mapping-table/ - lyricist" xr:uid="{D4CAFE49-3EF8-4608-B40F-486F9EE94C3A}"/>
-    <hyperlink ref="A34" r:id="rId33" location="mediatype" display="https://docs.mp3tag.de/mapping-table/ - mediatype" xr:uid="{72C92CD4-8076-4E7C-A327-4C849A509D31}"/>
-    <hyperlink ref="A35" r:id="rId34" location="mixartist" display="https://docs.mp3tag.de/mapping-table/ - mixartist" xr:uid="{884B2AAA-BA90-4E70-A29B-B46E1A8FA2FD}"/>
-    <hyperlink ref="A36" r:id="rId35" location="mood" display="https://docs.mp3tag.de/mapping-table/ - mood" xr:uid="{BD4BD98F-C054-4622-B912-18E0699C13E0}"/>
-    <hyperlink ref="A37" r:id="rId36" location="movementname" display="https://docs.mp3tag.de/mapping-table/ - movementname" xr:uid="{2E389684-6C58-4327-BB1F-74A789A5A24A}"/>
-    <hyperlink ref="A38" r:id="rId37" location="movement" display="https://docs.mp3tag.de/mapping-table/ - movement" xr:uid="{367D7AFC-2DE7-4815-9D9E-590484F22F74}"/>
-    <hyperlink ref="A39" r:id="rId38" location="movementtotal" display="https://docs.mp3tag.de/mapping-table/ - movementtotal" xr:uid="{4CC3A6EC-A4A3-4F14-8B38-8B03E7C5A221}"/>
-    <hyperlink ref="A40" r:id="rId39" location="musiciancredits" display="https://docs.mp3tag.de/mapping-table/ - musiciancredits" xr:uid="{E8F03750-513A-42DE-9CAA-9D6F59E55E59}"/>
-    <hyperlink ref="A41" r:id="rId40" location="narrator" display="https://docs.mp3tag.de/mapping-table/ - narrator" xr:uid="{2673A136-7B7F-4A7A-849C-C8181635CD91}"/>
-    <hyperlink ref="A42" r:id="rId41" location="netradioowner" display="https://docs.mp3tag.de/mapping-table/ - netradioowner" xr:uid="{78B7FE28-5592-4C47-950E-39F71C59C701}"/>
-    <hyperlink ref="A43" r:id="rId42" location="netradiostation" display="https://docs.mp3tag.de/mapping-table/ - netradiostation" xr:uid="{312816FE-84C4-4151-B3D0-9644DA417334}"/>
-    <hyperlink ref="A44" r:id="rId43" location="origalbum" display="https://docs.mp3tag.de/mapping-table/ - origalbum" xr:uid="{254E779A-86DC-418F-BEA7-8E07FEBB3BD5}"/>
-    <hyperlink ref="A45" r:id="rId44" location="origartist" display="https://docs.mp3tag.de/mapping-table/ - origartist" xr:uid="{ECC23B0C-0902-43CA-BFF0-1B9011C0C144}"/>
-    <hyperlink ref="A46" r:id="rId45" location="origfilename" display="https://docs.mp3tag.de/mapping-table/ - origfilename" xr:uid="{73F540E1-D49E-45BA-9231-5B03E4FA7030}"/>
-    <hyperlink ref="A47" r:id="rId46" location="origlyricist" display="https://docs.mp3tag.de/mapping-table/ - origlyricist" xr:uid="{D5DF5E2D-AD24-46C7-8E6C-EFE57225E1D3}"/>
-    <hyperlink ref="A48" r:id="rId47" location="origyear" display="https://docs.mp3tag.de/mapping-table/ - origyear" xr:uid="{8D92F6A2-E133-4A9C-A8F0-BE32AB11911E}"/>
-    <hyperlink ref="A49" r:id="rId48" location="podcast" display="https://docs.mp3tag.de/mapping-table/ - podcast" xr:uid="{D6A2B856-3052-4272-8A59-42D2FA8FEBE7}"/>
-    <hyperlink ref="A50" r:id="rId49" location="podcastcategory" display="https://docs.mp3tag.de/mapping-table/ - podcastcategory" xr:uid="{312CECDF-3DAE-446A-B877-54FC951C31B1}"/>
-    <hyperlink ref="A51" r:id="rId50" location="podcastdesc" display="https://docs.mp3tag.de/mapping-table/ - podcastdesc" xr:uid="{EF7F19A1-BB0A-4A98-9036-FA2A3304405E}"/>
-    <hyperlink ref="A52" r:id="rId51" location="podcastid" display="https://docs.mp3tag.de/mapping-table/ - podcastid" xr:uid="{63B051D1-FA17-4259-9428-2F8A04B4C47E}"/>
-    <hyperlink ref="A53" r:id="rId52" location="podcastkeywords" display="https://docs.mp3tag.de/mapping-table/ - podcastkeywords" xr:uid="{07368C83-550F-4AD7-997D-CCB0EF1C764F}"/>
-    <hyperlink ref="A54" r:id="rId53" location="podcasturl" display="https://docs.mp3tag.de/mapping-table/ - podcasturl" xr:uid="{1DA981C9-688E-4D37-9CE1-383555777EE8}"/>
-    <hyperlink ref="A55" r:id="rId54" location="popularimeter" display="https://docs.mp3tag.de/mapping-table/ - popularimeter" xr:uid="{B03B2BE5-7536-4EA0-B6B2-674844BF0272}"/>
-    <hyperlink ref="A56" r:id="rId55" location="publisher" display="https://docs.mp3tag.de/mapping-table/ - publisher" xr:uid="{BF8CF9EC-BE10-4BBE-9AB0-3C1E62072FC0}"/>
-    <hyperlink ref="A57" r:id="rId56" location="rating-wmp" display="https://docs.mp3tag.de/mapping-table/ - rating-wmp" xr:uid="{689ADA24-B501-4D03-A713-E940351BC63D}"/>
-    <hyperlink ref="A58" r:id="rId57" location="releasetime" display="https://docs.mp3tag.de/mapping-table/ - releasetime" xr:uid="{D1D489F6-BCE9-476A-9020-487191417660}"/>
-    <hyperlink ref="A59" r:id="rId58" location="setsubtitle" display="https://docs.mp3tag.de/mapping-table/ - setsubtitle" xr:uid="{4241860A-C6AA-41FD-8049-047F2427F1C4}"/>
-    <hyperlink ref="A60" r:id="rId59" location="subtitle" display="https://docs.mp3tag.de/mapping-table/ - subtitle" xr:uid="{CB4396AC-80C4-4BAC-B66A-B83DD57195B3}"/>
-    <hyperlink ref="A61" r:id="rId60" location="taggingtime" display="https://docs.mp3tag.de/mapping-table/ - taggingtime" xr:uid="{17CC58FA-9908-441F-95A8-26B2B5C0334E}"/>
-    <hyperlink ref="A62" r:id="rId61" location="title" display="https://docs.mp3tag.de/mapping-table/ - title" xr:uid="{E8B9A36C-D901-4774-A2F5-FB9614F83254}"/>
-    <hyperlink ref="A63" r:id="rId62" location="titlesort" display="https://docs.mp3tag.de/mapping-table/ - titlesort" xr:uid="{F8C9CB6C-61E1-45AD-95E8-715B3B24D063}"/>
-    <hyperlink ref="A64" r:id="rId63" location="track" display="https://docs.mp3tag.de/mapping-table/ - track" xr:uid="{64A1C198-320D-4F2B-942E-644F07501971}"/>
-    <hyperlink ref="A65" r:id="rId64" location="uniquefileid" display="https://docs.mp3tag.de/mapping-table/ - uniquefileid" xr:uid="{52A4386A-4EBF-4143-A42E-0B5C68437A53}"/>
-    <hyperlink ref="A66" r:id="rId65" location="unsyncedlyrics" display="https://docs.mp3tag.de/mapping-table/ - unsyncedlyrics" xr:uid="{FBCDB365-F1A7-4BED-9E2A-AB86B4C5A024}"/>
-    <hyperlink ref="A67" r:id="rId66" location="www" display="https://docs.mp3tag.de/mapping-table/ - www" xr:uid="{9565592F-DB1F-4DEC-9E5B-F68BA177D452}"/>
-    <hyperlink ref="A68" r:id="rId67" location="wwwartist" display="https://docs.mp3tag.de/mapping-table/ - wwwartist" xr:uid="{3DC8A188-3768-4DE1-B1B2-8A3DA01A9B18}"/>
-    <hyperlink ref="A69" r:id="rId68" location="wwwaudiofile" display="https://docs.mp3tag.de/mapping-table/ - wwwaudiofile" xr:uid="{9228F134-3438-4D14-BDBB-B6D0F44D844A}"/>
-    <hyperlink ref="A70" r:id="rId69" location="wwwaudiosource" display="https://docs.mp3tag.de/mapping-table/ - wwwaudiosource" xr:uid="{1706FED3-F376-4AA7-8521-F1CC52E62E4A}"/>
-    <hyperlink ref="A71" r:id="rId70" location="wwwcommercialinfo" display="https://docs.mp3tag.de/mapping-table/ - wwwcommercialinfo" xr:uid="{A919EF6D-CEA1-4B05-935C-D58916BCB6C2}"/>
-    <hyperlink ref="A72" r:id="rId71" location="wwwcopyright" display="https://docs.mp3tag.de/mapping-table/ - wwwcopyright" xr:uid="{9DD1B73C-B0D5-4DA2-AFE0-5CF5BA8DD8D6}"/>
-    <hyperlink ref="A73" r:id="rId72" location="wwwpayment" display="https://docs.mp3tag.de/mapping-table/ - wwwpayment" xr:uid="{8C31718B-C970-439D-8746-8DF0017E2062}"/>
-    <hyperlink ref="A74" r:id="rId73" location="wwwpublisher" display="https://docs.mp3tag.de/mapping-table/ - wwwpublisher" xr:uid="{4D7BC77C-CB64-4CE3-9E79-5CB3B18F40C8}"/>
-    <hyperlink ref="A75" r:id="rId74" location="wwwradiopage" display="https://docs.mp3tag.de/mapping-table/ - wwwradiopage" xr:uid="{1F4697C3-8002-4737-BEA5-61C083D6DFA7}"/>
-    <hyperlink ref="A76" r:id="rId75" location="year" display="https://docs.mp3tag.de/mapping-table/ - year" xr:uid="{EFD75774-1055-4393-9EE4-AE9C5D250623}"/>
-    <hyperlink ref="A77" r:id="rId76" location="other-fields" display="https://docs.mp3tag.de/mapping-table/ - other-fields" xr:uid="{1BFE8748-7918-4A56-B501-9123FF2BC9AD}"/>
+    <hyperlink ref="A9" r:id="rId7" location="artist" display="https://docs.mp3tag.de/mapping-table/ - artist" xr:uid="{236B4608-7E32-4791-82B8-461C2ED1E009}"/>
+    <hyperlink ref="A10" r:id="rId8" location="artistsort" display="https://docs.mp3tag.de/mapping-table/ - artistsort" xr:uid="{F7E32035-C4EE-47AD-AB96-5FFB1EE40B6E}"/>
+    <hyperlink ref="A11" r:id="rId9" location="bpm" display="https://docs.mp3tag.de/mapping-table/ - bpm" xr:uid="{417BD8A8-54C5-4CA8-83B7-DD44A0D62B9D}"/>
+    <hyperlink ref="A12" r:id="rId10" location="comment" display="https://docs.mp3tag.de/mapping-table/ - comment" xr:uid="{EC4C54EF-C90D-48CF-8E6D-F63990567046}"/>
+    <hyperlink ref="A13" r:id="rId11" location="compilation" display="https://docs.mp3tag.de/mapping-table/ - compilation" xr:uid="{6767F38C-7169-4224-AFB8-A2FB203B1765}"/>
+    <hyperlink ref="A14" r:id="rId12" location="composer" display="https://docs.mp3tag.de/mapping-table/ - composer" xr:uid="{F59BF3E6-5073-42E9-BABC-679118C66E9A}"/>
+    <hyperlink ref="A15" r:id="rId13" location="composersort" display="https://docs.mp3tag.de/mapping-table/ - composersort" xr:uid="{EA1C71C2-F1C1-4694-9360-8205B00E8EA9}"/>
+    <hyperlink ref="A16" r:id="rId14" location="conductor" display="https://docs.mp3tag.de/mapping-table/ - conductor" xr:uid="{938268DC-3D45-4CE9-AE53-1A16ADBD5E92}"/>
+    <hyperlink ref="A17" r:id="rId15" location="contentgroup" display="https://docs.mp3tag.de/mapping-table/ - contentgroup" xr:uid="{325795C6-8803-429C-B96B-1EE71D190774}"/>
+    <hyperlink ref="A18" r:id="rId16" location="copyright" display="https://docs.mp3tag.de/mapping-table/ - copyright" xr:uid="{ECE81421-7610-4DC4-A813-351A7D2DF86F}"/>
+    <hyperlink ref="A19" r:id="rId17" location="date" display="https://docs.mp3tag.de/mapping-table/ - date" xr:uid="{C6D0C948-83BA-4EA8-8E18-B41689071623}"/>
+    <hyperlink ref="A20" r:id="rId18" location="description" display="https://docs.mp3tag.de/mapping-table/ - description" xr:uid="{92DAA412-9AE3-40D7-9EC5-21C4E42A776A}"/>
+    <hyperlink ref="A21" r:id="rId19" location="discnumber" display="https://docs.mp3tag.de/mapping-table/ - discnumber" xr:uid="{40CCC2AF-B3A2-4C9F-9DBF-27338C7896EA}"/>
+    <hyperlink ref="A22" r:id="rId20" location="encodedby" display="https://docs.mp3tag.de/mapping-table/ - encodedby" xr:uid="{4AB3273E-8541-486F-ABFF-C983DC6AE843}"/>
+    <hyperlink ref="A23" r:id="rId21" location="encodersettings" display="https://docs.mp3tag.de/mapping-table/ - encodersettings" xr:uid="{649B9604-04F5-4FE7-9842-5E27EFAE13E9}"/>
+    <hyperlink ref="A24" r:id="rId22" location="encodingtime" display="https://docs.mp3tag.de/mapping-table/ - encodingtime" xr:uid="{2AA00A50-84DF-4B28-B1CD-47E32FFBD2E9}"/>
+    <hyperlink ref="A25" r:id="rId23" location="fileowner" display="https://docs.mp3tag.de/mapping-table/ - fileowner" xr:uid="{B2201482-05EB-4062-A3F1-7FF04270E1E6}"/>
+    <hyperlink ref="A26" r:id="rId24" location="filetype" display="https://docs.mp3tag.de/mapping-table/ - filetype" xr:uid="{A18848A7-32AD-4B93-8679-B4FACBF6B1F0}"/>
+    <hyperlink ref="A27" r:id="rId25" location="genre" display="https://docs.mp3tag.de/mapping-table/ - genre" xr:uid="{06F89C2D-E212-45FA-95F6-ED590312B1AF}"/>
+    <hyperlink ref="A28" r:id="rId26" location="grouping" display="https://docs.mp3tag.de/mapping-table/ - grouping" xr:uid="{32419C34-9D9D-44BF-8A04-38F95F4C0E8F}"/>
+    <hyperlink ref="A29" r:id="rId27" location="initialkey" display="https://docs.mp3tag.de/mapping-table/ - initialkey" xr:uid="{D5949161-FC64-4D97-9683-CD512F59BBE5}"/>
+    <hyperlink ref="A30" r:id="rId28" location="involvedpeople" display="https://docs.mp3tag.de/mapping-table/ - involvedpeople" xr:uid="{29B7C220-BDD5-4964-A2CD-D239D4AFB52C}"/>
+    <hyperlink ref="A31" r:id="rId29" location="isrc" display="https://docs.mp3tag.de/mapping-table/ - isrc" xr:uid="{7B9290C2-318D-4750-B2D8-0254EC4D9E19}"/>
+    <hyperlink ref="A32" r:id="rId30" location="language" display="https://docs.mp3tag.de/mapping-table/ - language" xr:uid="{FD666EB8-5DD8-4502-A23A-37E947DECDBD}"/>
+    <hyperlink ref="A33" r:id="rId31" location="length" display="https://docs.mp3tag.de/mapping-table/ - length" xr:uid="{A6E54695-7179-42BB-AE44-2501173B82AA}"/>
+    <hyperlink ref="A34" r:id="rId32" location="lyricist" display="https://docs.mp3tag.de/mapping-table/ - lyricist" xr:uid="{D4CAFE49-3EF8-4608-B40F-486F9EE94C3A}"/>
+    <hyperlink ref="A35" r:id="rId33" location="mediatype" display="https://docs.mp3tag.de/mapping-table/ - mediatype" xr:uid="{72C92CD4-8076-4E7C-A327-4C849A509D31}"/>
+    <hyperlink ref="A36" r:id="rId34" location="mixartist" display="https://docs.mp3tag.de/mapping-table/ - mixartist" xr:uid="{884B2AAA-BA90-4E70-A29B-B46E1A8FA2FD}"/>
+    <hyperlink ref="A37" r:id="rId35" location="mood" display="https://docs.mp3tag.de/mapping-table/ - mood" xr:uid="{BD4BD98F-C054-4622-B912-18E0699C13E0}"/>
+    <hyperlink ref="A38" r:id="rId36" location="movementname" display="https://docs.mp3tag.de/mapping-table/ - movementname" xr:uid="{2E389684-6C58-4327-BB1F-74A789A5A24A}"/>
+    <hyperlink ref="A39" r:id="rId37" location="movement" display="https://docs.mp3tag.de/mapping-table/ - movement" xr:uid="{367D7AFC-2DE7-4815-9D9E-590484F22F74}"/>
+    <hyperlink ref="A40" r:id="rId38" location="movementtotal" display="https://docs.mp3tag.de/mapping-table/ - movementtotal" xr:uid="{4CC3A6EC-A4A3-4F14-8B38-8B03E7C5A221}"/>
+    <hyperlink ref="A41" r:id="rId39" location="musiciancredits" display="https://docs.mp3tag.de/mapping-table/ - musiciancredits" xr:uid="{E8F03750-513A-42DE-9CAA-9D6F59E55E59}"/>
+    <hyperlink ref="A42" r:id="rId40" location="narrator" display="https://docs.mp3tag.de/mapping-table/ - narrator" xr:uid="{2673A136-7B7F-4A7A-849C-C8181635CD91}"/>
+    <hyperlink ref="A43" r:id="rId41" location="netradioowner" display="https://docs.mp3tag.de/mapping-table/ - netradioowner" xr:uid="{78B7FE28-5592-4C47-950E-39F71C59C701}"/>
+    <hyperlink ref="A44" r:id="rId42" location="netradiostation" display="https://docs.mp3tag.de/mapping-table/ - netradiostation" xr:uid="{312816FE-84C4-4151-B3D0-9644DA417334}"/>
+    <hyperlink ref="A45" r:id="rId43" location="origalbum" display="https://docs.mp3tag.de/mapping-table/ - origalbum" xr:uid="{254E779A-86DC-418F-BEA7-8E07FEBB3BD5}"/>
+    <hyperlink ref="A46" r:id="rId44" location="origartist" display="https://docs.mp3tag.de/mapping-table/ - origartist" xr:uid="{ECC23B0C-0902-43CA-BFF0-1B9011C0C144}"/>
+    <hyperlink ref="A47" r:id="rId45" location="origfilename" display="https://docs.mp3tag.de/mapping-table/ - origfilename" xr:uid="{73F540E1-D49E-45BA-9231-5B03E4FA7030}"/>
+    <hyperlink ref="A48" r:id="rId46" location="origlyricist" display="https://docs.mp3tag.de/mapping-table/ - origlyricist" xr:uid="{D5DF5E2D-AD24-46C7-8E6C-EFE57225E1D3}"/>
+    <hyperlink ref="A49" r:id="rId47" location="origyear" display="https://docs.mp3tag.de/mapping-table/ - origyear" xr:uid="{8D92F6A2-E133-4A9C-A8F0-BE32AB11911E}"/>
+    <hyperlink ref="A50" r:id="rId48" location="podcast" display="https://docs.mp3tag.de/mapping-table/ - podcast" xr:uid="{D6A2B856-3052-4272-8A59-42D2FA8FEBE7}"/>
+    <hyperlink ref="A51" r:id="rId49" location="podcastcategory" display="https://docs.mp3tag.de/mapping-table/ - podcastcategory" xr:uid="{312CECDF-3DAE-446A-B877-54FC951C31B1}"/>
+    <hyperlink ref="A52" r:id="rId50" location="podcastdesc" display="https://docs.mp3tag.de/mapping-table/ - podcastdesc" xr:uid="{EF7F19A1-BB0A-4A98-9036-FA2A3304405E}"/>
+    <hyperlink ref="A53" r:id="rId51" location="podcastid" display="https://docs.mp3tag.de/mapping-table/ - podcastid" xr:uid="{63B051D1-FA17-4259-9428-2F8A04B4C47E}"/>
+    <hyperlink ref="A54" r:id="rId52" location="podcastkeywords" display="https://docs.mp3tag.de/mapping-table/ - podcastkeywords" xr:uid="{07368C83-550F-4AD7-997D-CCB0EF1C764F}"/>
+    <hyperlink ref="A55" r:id="rId53" location="podcasturl" display="https://docs.mp3tag.de/mapping-table/ - podcasturl" xr:uid="{1DA981C9-688E-4D37-9CE1-383555777EE8}"/>
+    <hyperlink ref="A56" r:id="rId54" location="popularimeter" display="https://docs.mp3tag.de/mapping-table/ - popularimeter" xr:uid="{B03B2BE5-7536-4EA0-B6B2-674844BF0272}"/>
+    <hyperlink ref="A57" r:id="rId55" location="publisher" display="https://docs.mp3tag.de/mapping-table/ - publisher" xr:uid="{BF8CF9EC-BE10-4BBE-9AB0-3C1E62072FC0}"/>
+    <hyperlink ref="A58" r:id="rId56" location="rating-wmp" display="https://docs.mp3tag.de/mapping-table/ - rating-wmp" xr:uid="{689ADA24-B501-4D03-A713-E940351BC63D}"/>
+    <hyperlink ref="A59" r:id="rId57" location="releasetime" display="https://docs.mp3tag.de/mapping-table/ - releasetime" xr:uid="{D1D489F6-BCE9-476A-9020-487191417660}"/>
+    <hyperlink ref="A60" r:id="rId58" location="setsubtitle" display="https://docs.mp3tag.de/mapping-table/ - setsubtitle" xr:uid="{4241860A-C6AA-41FD-8049-047F2427F1C4}"/>
+    <hyperlink ref="A61" r:id="rId59" location="subtitle" display="https://docs.mp3tag.de/mapping-table/ - subtitle" xr:uid="{CB4396AC-80C4-4BAC-B66A-B83DD57195B3}"/>
+    <hyperlink ref="A62" r:id="rId60" location="taggingtime" display="https://docs.mp3tag.de/mapping-table/ - taggingtime" xr:uid="{17CC58FA-9908-441F-95A8-26B2B5C0334E}"/>
+    <hyperlink ref="A63" r:id="rId61" location="title" display="https://docs.mp3tag.de/mapping-table/ - title" xr:uid="{E8B9A36C-D901-4774-A2F5-FB9614F83254}"/>
+    <hyperlink ref="A64" r:id="rId62" location="titlesort" display="https://docs.mp3tag.de/mapping-table/ - titlesort" xr:uid="{F8C9CB6C-61E1-45AD-95E8-715B3B24D063}"/>
+    <hyperlink ref="A65" r:id="rId63" location="track" display="https://docs.mp3tag.de/mapping-table/ - track" xr:uid="{64A1C198-320D-4F2B-942E-644F07501971}"/>
+    <hyperlink ref="A66" r:id="rId64" location="uniquefileid" display="https://docs.mp3tag.de/mapping-table/ - uniquefileid" xr:uid="{52A4386A-4EBF-4143-A42E-0B5C68437A53}"/>
+    <hyperlink ref="A67" r:id="rId65" location="unsyncedlyrics" display="https://docs.mp3tag.de/mapping-table/ - unsyncedlyrics" xr:uid="{FBCDB365-F1A7-4BED-9E2A-AB86B4C5A024}"/>
+    <hyperlink ref="A68" r:id="rId66" location="www" display="https://docs.mp3tag.de/mapping-table/ - www" xr:uid="{9565592F-DB1F-4DEC-9E5B-F68BA177D452}"/>
+    <hyperlink ref="A69" r:id="rId67" location="wwwartist" display="https://docs.mp3tag.de/mapping-table/ - wwwartist" xr:uid="{3DC8A188-3768-4DE1-B1B2-8A3DA01A9B18}"/>
+    <hyperlink ref="A70" r:id="rId68" location="wwwaudiofile" display="https://docs.mp3tag.de/mapping-table/ - wwwaudiofile" xr:uid="{9228F134-3438-4D14-BDBB-B6D0F44D844A}"/>
+    <hyperlink ref="A71" r:id="rId69" location="wwwaudiosource" display="https://docs.mp3tag.de/mapping-table/ - wwwaudiosource" xr:uid="{1706FED3-F376-4AA7-8521-F1CC52E62E4A}"/>
+    <hyperlink ref="A72" r:id="rId70" location="wwwcommercialinfo" display="https://docs.mp3tag.de/mapping-table/ - wwwcommercialinfo" xr:uid="{A919EF6D-CEA1-4B05-935C-D58916BCB6C2}"/>
+    <hyperlink ref="A73" r:id="rId71" location="wwwcopyright" display="https://docs.mp3tag.de/mapping-table/ - wwwcopyright" xr:uid="{9DD1B73C-B0D5-4DA2-AFE0-5CF5BA8DD8D6}"/>
+    <hyperlink ref="A74" r:id="rId72" location="wwwpayment" display="https://docs.mp3tag.de/mapping-table/ - wwwpayment" xr:uid="{8C31718B-C970-439D-8746-8DF0017E2062}"/>
+    <hyperlink ref="A75" r:id="rId73" location="wwwpublisher" display="https://docs.mp3tag.de/mapping-table/ - wwwpublisher" xr:uid="{4D7BC77C-CB64-4CE3-9E79-5CB3B18F40C8}"/>
+    <hyperlink ref="A76" r:id="rId74" location="wwwradiopage" display="https://docs.mp3tag.de/mapping-table/ - wwwradiopage" xr:uid="{1F4697C3-8002-4737-BEA5-61C083D6DFA7}"/>
+    <hyperlink ref="A77" r:id="rId75" location="year" display="https://docs.mp3tag.de/mapping-table/ - year" xr:uid="{EFD75774-1055-4393-9EE4-AE9C5D250623}"/>
+    <hyperlink ref="A78" r:id="rId76" location="other-fields" display="https://docs.mp3tag.de/mapping-table/ - other-fields" xr:uid="{1BFE8748-7918-4A56-B501-9123FF2BC9AD}"/>
+    <hyperlink ref="F8" r:id="rId77" xr:uid="{F107A0CE-F201-4458-AC66-9DF6DC035E71}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
